--- a/data/trans_dic/IP1021_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1021_2023-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen dolor crónico</t>
+          <t>Menores que padecen dolor crónico (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 5,89</t>
+          <t>0,37; 5,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,58</t>
+          <t>0,44; 4,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,79</t>
+          <t>0,68; 3,7</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 5,42</t>
+          <t>0,45; 5,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,38</t>
+          <t>0,0; 7,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 4,84</t>
+          <t>0,69; 4,79</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,78</t>
+          <t>0,0; 3,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,82</t>
+          <t>0,0; 9,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 5,46</t>
+          <t>0,33; 5,07</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,05</t>
+          <t>0,3; 3,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,15</t>
+          <t>0,37; 3,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,31</t>
+          <t>0,53; 2,42</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,1; 8,3</t>
+          <t>1,99; 8,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 5,03</t>
+          <t>0,4; 4,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,95</t>
+          <t>1,37; 4,83</t>
         </is>
       </c>
     </row>
@@ -821,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,53</t>
+          <t>0,0; 6,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,01</t>
+          <t>0,0; 9,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,28; 5,66</t>
+          <t>0,28; 5,55</t>
         </is>
       </c>
     </row>
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,06</t>
+          <t>1,21; 2,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,86</t>
+          <t>1,03; 2,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,57</t>
+          <t>1,29; 2,51</t>
         </is>
       </c>
     </row>
@@ -905,4 +906,602 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen dolor crónico (tasa de respuesta: 99,95%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2316</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4312</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>387; 5876</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>594; 6340</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1636; 8916</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2136</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3936</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>422; 4832</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 7117</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1308; 9119</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1563</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1948</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2017</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5890</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>386; 5865</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2465</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2647</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5112</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>647; 6602</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>818; 7706</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2301; 10554</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>5308</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2715</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>8022</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2382; 9779</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>657; 7257</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3869; 13622</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1367</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2496</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4343</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 6726</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>396; 7821</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>13084</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>12743</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>25827</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>7965; 19026</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>7691; 21345</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>18123; 35242</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1021_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1021_2023-Clase-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 5,63</t>
+          <t>0,7; 5,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,65</t>
+          <t>0,44; 4,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,7</t>
+          <t>0,7; 4,17</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 5,1</t>
+          <t>0,44; 5,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,45</t>
+          <t>0,0; 7,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,79</t>
+          <t>0,68; 4,75</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,89</t>
+          <t>0,0; 3,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,22</t>
+          <t>0,0; 8,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 5,07</t>
+          <t>0,31; 4,79</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,03</t>
+          <t>0,3; 3,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,53</t>
+          <t>0,37; 3,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,42</t>
+          <t>0,53; 2,22</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,99; 8,19</t>
+          <t>2,26; 8,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 4,46</t>
+          <t>0,42; 4,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,83</t>
+          <t>1,53; 4,92</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,3</t>
+          <t>0,0; 5,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,34</t>
+          <t>0,0; 8,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,28; 5,55</t>
+          <t>0,28; 6,22</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,89</t>
+          <t>1,31; 3,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,85</t>
+          <t>1,01; 2,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,51</t>
+          <t>1,32; 2,6</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>387; 5876</t>
+          <t>728; 5896</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>594; 6340</t>
+          <t>602; 6509</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1636; 8916</t>
+          <t>1691; 10035</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>422; 4832</t>
+          <t>421; 4972</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 7117</t>
+          <t>0; 7260</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1308; 9119</t>
+          <t>1287; 9029</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2017</t>
+          <t>0; 1998</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5890</t>
+          <t>0; 5282</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>386; 5865</t>
+          <t>358; 5546</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>647; 6602</t>
+          <t>655; 6770</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>818; 7706</t>
+          <t>816; 6862</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2301; 10554</t>
+          <t>2313; 9692</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2382; 9779</t>
+          <t>2696; 9710</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>657; 7257</t>
+          <t>678; 7688</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3869; 13622</t>
+          <t>4319; 13877</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4343</t>
+          <t>0; 3891</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6726</t>
+          <t>0; 6414</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>396; 7821</t>
+          <t>393; 8769</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>7965; 19026</t>
+          <t>8588; 20603</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7691; 21345</t>
+          <t>7545; 21141</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18123; 35242</t>
+          <t>18504; 36586</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1021_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1021_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 5,64</t>
+          <t>0,43; 5,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,77</t>
+          <t>0,34; 6,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,17</t>
+          <t>0,66; 3,94</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 5,25</t>
+          <t>0,0; 7,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,6</t>
+          <t>0,36; 5,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,75</t>
+          <t>0,74; 4,71</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,85</t>
+          <t>0,0; 9,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,27</t>
+          <t>0,0; 3,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 4,79</t>
+          <t>0,32; 5,32</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,11</t>
+          <t>0,34; 3,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,14</t>
+          <t>0,41; 3,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,22</t>
+          <t>0,53; 2,58</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,26; 8,13</t>
+          <t>0,37; 4,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,73</t>
+          <t>2,17; 8,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,92</t>
+          <t>1,53; 5,15</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,65</t>
+          <t>0,0; 9,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,91</t>
+          <t>0,0; 5,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,28; 6,22</t>
+          <t>0,25; 4,8</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,13</t>
+          <t>0,92; 2,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,82</t>
+          <t>1,35; 3,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,6</t>
+          <t>1,3; 2,61</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2316</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>4100</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>728; 5896</t>
+          <t>522; 6164</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>602; 6509</t>
+          <t>346; 6314</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1691; 10035</t>
+          <t>1487; 8853</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1969</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2136</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>3734</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>421; 4972</t>
+          <t>0; 6475</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 7260</t>
+          <t>352; 5191</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1287; 9029</t>
+          <t>1399; 8846</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1563</t>
+          <t>344</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>1779</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1998</t>
+          <t>0; 5250</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5282</t>
+          <t>0; 1776</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>358; 5546</t>
+          <t>354; 5876</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2465</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2647</t>
+          <t>2572</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>4912</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>655; 6770</t>
+          <t>689; 6418</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>816; 6862</t>
+          <t>734; 6544</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2313; 9692</t>
+          <t>2027; 9807</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>2445</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>5445</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8022</t>
+          <t>7890</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2696; 9710</t>
+          <t>554; 7277</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>678; 7688</t>
+          <t>2579; 10175</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4319; 13877</t>
+          <t>4090; 13759</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>978</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2496</t>
+          <t>2085</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3891</t>
+          <t>0; 6372</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6414</t>
+          <t>0; 3952</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>393; 8769</t>
+          <t>346; 6657</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>13084</t>
+          <t>11263</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>12743</t>
+          <t>13236</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>25827</t>
+          <t>24500</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>8588; 20603</t>
+          <t>6336; 18640</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7545; 21141</t>
+          <t>8353; 20381</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18504; 36586</t>
+          <t>16963; 34160</t>
         </is>
       </c>
     </row>
